--- a/test/fixtures/functions.xlsx
+++ b/test/fixtures/functions.xlsx
@@ -413,6 +413,7 @@
       </c>
       <c r="B2">
         <f>LOG10(A2)*2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -421,6 +422,7 @@
       </c>
       <c r="B3">
         <f>LOG10(A3)*2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -429,6 +431,7 @@
       </c>
       <c r="B4">
         <f>LOG10(A4)*2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -437,6 +440,7 @@
       </c>
       <c r="B5">
         <f>LOG10(A5)*2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -445,6 +449,7 @@
       </c>
       <c r="B6">
         <f>LOG10(A6)*2</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
